--- a/Методы прогнозной аналитики в задача информационой безопасности/Практика 3/Практика 3.xlsx
+++ b/Методы прогнозной аналитики в задача информационой безопасности/Практика 3/Практика 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\University\Методы прогнозной аналитики в задача информационой безопасности\Практика 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4EF1ACB-3C7F-4DF2-8F95-AEB35CCFFBF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1C2D31-7608-4A2C-916F-D359FE7B8283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Фостер Стюарт" sheetId="4" r:id="rId3"/>
     <sheet name="Прогноз 60 39" sheetId="5" r:id="rId4"/>
     <sheet name="Итоги 60 39" sheetId="6" r:id="rId5"/>
+    <sheet name="Прирост цепной и абсолютный " sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8492" uniqueCount="1228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8521" uniqueCount="1252">
   <si>
     <t>javax.faces.component.UIPanel@7d089a51</t>
   </si>
@@ -3547,6 +3548,9 @@
     <t>t</t>
   </si>
   <si>
+    <t>Инциденты y_t</t>
+  </si>
+  <si>
     <t>Максимум до t</t>
   </si>
   <si>
@@ -3565,12 +3569,36 @@
     <t>1/t</t>
   </si>
   <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> b</t>
+  </si>
+  <si>
+    <t>Неделя t</t>
+  </si>
+  <si>
+    <t>Дата недели</t>
+  </si>
+  <si>
+    <t>Факт (только 1–60)</t>
+  </si>
+  <si>
+    <t>Свободный член a</t>
+  </si>
+  <si>
+    <t>Вклад наклона b·t</t>
+  </si>
+  <si>
+    <t>Линия тренда a+b·t</t>
+  </si>
+  <si>
+    <t>Период</t>
+  </si>
+  <si>
     <t>Номер недели</t>
   </si>
   <si>
-    <t>Дата недели</t>
-  </si>
-  <si>
     <t>Известное x_t</t>
   </si>
   <si>
@@ -3694,43 +3722,89 @@
     <t>Прогноз на неделю 99</t>
   </si>
   <si>
-    <t>Неделя t</t>
-  </si>
-  <si>
-    <t>Факт (только 1–60)</t>
-  </si>
-  <si>
-    <t>Свободный член a</t>
-  </si>
-  <si>
-    <t>Вклад наклона b·t</t>
-  </si>
-  <si>
-    <t>Линия тренда a+b·t</t>
-  </si>
-  <si>
-    <t>Период</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>Инциденты y_t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> b</t>
+    <t>Номер t</t>
+  </si>
+  <si>
+    <t>Факт 1–60</t>
+  </si>
+  <si>
+    <t>Цепной абсолютный прирост</t>
+  </si>
+  <si>
+    <t>Средний абсолютный прирост</t>
+  </si>
+  <si>
+    <t>Прогноз без округления</t>
+  </si>
+  <si>
+    <t>Прогноз, инциденты</t>
+  </si>
+  <si>
+    <t>Факт 61–99 для проверки</t>
+  </si>
+  <si>
+    <t>Обучающих наблюдений n</t>
+  </si>
+  <si>
+    <t>Первое значение y₁</t>
+  </si>
+  <si>
+    <t>Последнее значение y₆₀</t>
+  </si>
+  <si>
+    <t>Средний абсолютный прирост Δ̄</t>
+  </si>
+  <si>
+    <t>СКО цепных приростов</t>
+  </si>
+  <si>
+    <t>Минимальный прирост</t>
+  </si>
+  <si>
+    <t>Максимальный прирост</t>
+  </si>
+  <si>
+    <t>Прогноз на t=61, без округления</t>
+  </si>
+  <si>
+    <t>Прогноз на t=99, без округления</t>
+  </si>
+  <si>
+    <t>MAE по 39 контрольным строкам</t>
+  </si>
+  <si>
+    <t>WAPE по 39 контрольным строкам, %</t>
+  </si>
+  <si>
+    <t>Среднее y₁…y₂₀</t>
+  </si>
+  <si>
+    <t>Среднее y₂₁…y₄₀</t>
+  </si>
+  <si>
+    <t>Среднее y₄₁…y₆₀</t>
+  </si>
+  <si>
+    <t>Формула: ŷ₆₀₊ₕ = y₆₀ + h·Δ̄, где h=1…39.</t>
+  </si>
+  <si>
+    <t>Контрольные факты не участвуют в расчёте Δ̄ и прогноза.</t>
+  </si>
+  <si>
+    <t>Ограничение: низкое y₆₀ делает средний прирост близким к нулю.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0000000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0000000000"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3763,10 +3837,40 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF243247"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF697586"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFC0473D"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3781,13 +3885,32 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF3FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F7F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -3866,7 +3989,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3908,10 +4031,29 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -4724,7 +4866,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E026-4948-8962-B7E89529B700}"/>
+              <c16:uniqueId val="{00000000-2E48-458C-87F1-15792978B7FE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5501,7 +5643,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CD31-428A-8DF0-6C3D350F4D92}"/>
+              <c16:uniqueId val="{00000000-1AFD-457E-BFAF-34CDE6D78005}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6137,7 +6279,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-CD31-428A-8DF0-6C3D350F4D92}"/>
+              <c16:uniqueId val="{00000001-1AFD-457E-BFAF-34CDE6D78005}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6301,7 +6443,6 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
-  <c:userShapes r:id="rId1"/>
 </c:chartSpace>
 </file>
 
@@ -6319,6 +6460,7 @@
           <a:lstStyle/>
           <a:p>
             <a:r>
+              <a:rPr lang="ru-RU"/>
               <a:t>Известный ряд, факт и прогноз</a:t>
             </a:r>
           </a:p>
@@ -6839,7 +6981,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-48E2-4E91-9F2E-93849B199475}"/>
+              <c16:uniqueId val="{00000000-2922-427E-AF02-1C7BBCC90178}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7287,7 +7429,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-48E2-4E91-9F2E-93849B199475}"/>
+              <c16:uniqueId val="{00000001-2922-427E-AF02-1C7BBCC90178}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7915,7 +8057,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-48E2-4E91-9F2E-93849B199475}"/>
+              <c16:uniqueId val="{00000002-2922-427E-AF02-1C7BBCC90178}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8023,6 +8165,7 @@
           <a:lstStyle/>
           <a:p>
             <a:r>
+              <a:rPr lang="ru-RU"/>
               <a:t>Накопление прогноза и прироста</a:t>
             </a:r>
           </a:p>
@@ -8303,7 +8446,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DCC8-4078-9B2A-2907A2565765}"/>
+              <c16:uniqueId val="{00000000-45DB-4D45-AA37-0FE90EB579C1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8574,7 +8717,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-DCC8-4078-9B2A-2907A2565765}"/>
+              <c16:uniqueId val="{00000001-45DB-4D45-AA37-0FE90EB579C1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8682,6 +8825,7 @@
           <a:lstStyle/>
           <a:p>
             <a:r>
+              <a:rPr lang="ru-RU"/>
               <a:t>Цепной и базисный темпы роста</a:t>
             </a:r>
           </a:p>
@@ -8962,7 +9106,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-51B8-4097-A092-1A3FE93E56A6}"/>
+              <c16:uniqueId val="{00000000-75F3-4745-916D-74A684F564EC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9233,7 +9377,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-51B8-4097-A092-1A3FE93E56A6}"/>
+              <c16:uniqueId val="{00000001-75F3-4745-916D-74A684F564EC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9306,6 +9450,2634 @@
     <c:legend>
       <c:legendPos val="b"/>
       <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="ru-RU" sz="900">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>Прогноз по среднему абсолютному приросту</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Факт 1–60</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="2463AD"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Прирост цепной и абсолютный '!$A$2:$A$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="99"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Прирост цепной и абсолютный '!$C$2:$C$100</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="99"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B2C8-4A99-9BFC-3112E1B8E2FC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Прогноз, инциденты</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="E3A12B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Прирост цепной и абсолютный '!$A$2:$A$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="99"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Прирост цепной и абсолютный '!$G$2:$G$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="99"/>
+                <c:pt idx="59" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="60" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="61" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="62" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="63" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="64" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="65" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="66" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="67" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="68" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="69" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="70" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="71" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="72" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="73" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="74" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="75" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="76" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="77" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="78" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="79" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="80" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="81" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="82" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="83" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="84" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="85" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="86" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="87" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="88" formatCode="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="89" formatCode="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="90" formatCode="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="91" formatCode="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="92" formatCode="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="93" formatCode="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="94" formatCode="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="95" formatCode="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="96" formatCode="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="97" formatCode="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="98" formatCode="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B2C8-4A99-9BFC-3112E1B8E2FC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Факт 61–99 для проверки</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="C0473D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Прирост цепной и абсолютный '!$A$2:$A$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="99"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Прирост цепной и абсолютный '!$H$2:$H$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="99"/>
+                <c:pt idx="60" formatCode="0">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="61" formatCode="0">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="62" formatCode="0">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="63" formatCode="0">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="64" formatCode="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="65" formatCode="0">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="66" formatCode="0">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="67" formatCode="0">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="68" formatCode="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="69" formatCode="0">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="70" formatCode="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="71" formatCode="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="72" formatCode="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="73" formatCode="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="74" formatCode="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="75" formatCode="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="76" formatCode="0">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="77" formatCode="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="78" formatCode="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="79" formatCode="0">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="80" formatCode="0">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="81" formatCode="0">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="82" formatCode="0">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="83" formatCode="0">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="84" formatCode="0">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="85" formatCode="0">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="86" formatCode="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="87" formatCode="0">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="88" formatCode="0">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="89" formatCode="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="90" formatCode="0">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="91" formatCode="0">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="92" formatCode="0">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="93" formatCode="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="94" formatCode="0">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="95" formatCode="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="96" formatCode="0">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="97" formatCode="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="98" formatCode="0">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-B2C8-4A99-9BFC-3112E1B8E2FC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:r>
+                  <a:rPr lang="ru-RU"/>
+                  <a:t>Номер наблюдения </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>t</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="675">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48672768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:r>
+                  <a:rPr lang="ru-RU"/>
+                  <a:t>Инциденты за неделю</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr>
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48650112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="ru-RU" sz="900">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>Цепные приросты первых 60 наблюдений</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Цепной абсолютный прирост</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="2463AD"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Прирост цепной и абсолютный '!$A$2:$A$61</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Прирост цепной и абсолютный '!$D$2:$D$61</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-4</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-5</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-7</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-6</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-4</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6259-4B89-A0E4-80D30F4D048E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Средний абсолютный прирост</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="C0473D"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Прирост цепной и абсолютный '!$A$2:$A$61</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Прирост цепной и абсолютный '!$E$2:$E$61</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="1">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.6949152542372881E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6259-4B89-A0E4-80D30F4D048E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:r>
+                  <a:rPr lang="ru-RU"/>
+                  <a:t>Номер наблюдения </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>t</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="675">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48672768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:r>
+                  <a:rPr lang="ru-RU"/>
+                  <a:t>Изменение, инцидентов</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr>
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48650112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
@@ -9406,773 +12178,10 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>192054</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>125963</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="301557" cy="409920"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBE6AB47-5187-4A8B-B0D9-05320255F554}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="9825911" y="125963"/>
-              <a:ext cx="301557" cy="409920"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:nary>
-                      <m:naryPr>
-                        <m:chr m:val="∑"/>
-                        <m:subHide m:val="on"/>
-                        <m:supHide m:val="on"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="ru-RU" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:naryPr>
-                      <m:sub/>
-                      <m:sup/>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑡</m:t>
-                        </m:r>
-                      </m:e>
-                    </m:nary>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="ru-RU" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBE6AB47-5187-4A8B-B0D9-05320255F554}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="9825911" y="125963"/>
-              <a:ext cx="301557" cy="409920"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="ru-RU" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>∑▒</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑡</a:t>
-              </a:r>
-              <a:endParaRPr lang="ru-RU" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>192055</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>102637</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="371447" cy="409920"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="TextBox 3">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8C6063D-A43B-41E8-A773-2C515DC7E807}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10479055" y="102637"/>
-              <a:ext cx="371447" cy="409920"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:nary>
-                      <m:naryPr>
-                        <m:chr m:val="∑"/>
-                        <m:subHide m:val="on"/>
-                        <m:supHide m:val="on"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="ru-RU" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:naryPr>
-                      <m:sub/>
-                      <m:sup/>
-                      <m:e>
-                        <m:sSup>
-                          <m:sSupPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="ru-RU" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSupPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑡</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sup>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>2</m:t>
-                            </m:r>
-                          </m:sup>
-                        </m:sSup>
-                      </m:e>
-                    </m:nary>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="ru-RU" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="TextBox 3">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8C6063D-A43B-41E8-A773-2C515DC7E807}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10479055" y="102637"/>
-              <a:ext cx="371447" cy="409920"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="ru-RU" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>∑▒</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑡</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="ru-RU" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>^</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>2</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="ru-RU" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-              <a:endParaRPr lang="ru-RU" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>199831</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>90974</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="370999" cy="409920"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="TextBox 4">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B674FC0-6B8C-448B-8603-1576935C1E41}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="11194402" y="90974"/>
-              <a:ext cx="370999" cy="409920"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:nary>
-                      <m:naryPr>
-                        <m:chr m:val="∑"/>
-                        <m:subHide m:val="on"/>
-                        <m:supHide m:val="on"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="ru-RU" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:naryPr>
-                      <m:sub/>
-                      <m:sup/>
-                      <m:e>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="ru-RU" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑦</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑡</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:e>
-                    </m:nary>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="ru-RU" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="TextBox 4">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B674FC0-6B8C-448B-8603-1576935C1E41}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="11194402" y="90974"/>
-              <a:ext cx="370999" cy="409920"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="ru-RU" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>∑▒</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑦</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="ru-RU" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>_</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑡</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="ru-RU" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-              <a:endParaRPr lang="ru-RU" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>274475</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>80088</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="430118" cy="409920"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="TextBox 5">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F439179-0C4B-4A57-B57C-7013F7CE8AFF}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="11976618" y="80088"/>
-              <a:ext cx="430118" cy="409920"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:nary>
-                      <m:naryPr>
-                        <m:chr m:val="∑"/>
-                        <m:subHide m:val="on"/>
-                        <m:supHide m:val="on"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="ru-RU" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:naryPr>
-                      <m:sub/>
-                      <m:sup/>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑡</m:t>
-                        </m:r>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="ru-RU" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑦</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑡</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:e>
-                    </m:nary>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="ru-RU" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="TextBox 5">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F439179-0C4B-4A57-B57C-7013F7CE8AFF}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="11976618" y="80088"/>
-              <a:ext cx="430118" cy="409920"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="ru-RU" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>∑▒〖</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑡𝑦</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="ru-RU" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>_</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑡</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="ru-RU" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> 〗</a:t>
-              </a:r>
-              <a:endParaRPr lang="ru-RU" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.61306</cdr:x>
-      <cdr:y>0.12735</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.61306</cdr:x>
-      <cdr:y>0.88429</cdr:y>
-    </cdr:to>
-    <cdr:cxnSp macro="">
-      <cdr:nvCxnSpPr>
-        <cdr:cNvPr id="7" name="Прямая соединительная линия 6">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7006B7CA-7B83-4974-8FAB-9929C06E5869}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvCxnSpPr/>
-      </cdr:nvCxnSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="9191737" y="696359"/>
-          <a:ext cx="0" cy="4139103"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:style>
-        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="3">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </cdr:style>
-    </cdr:cxnSp>
-  </cdr:relSizeAnchor>
-</c:userShapes>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -10277,6 +12286,83 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -42248,19 +44334,19 @@
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="8" width="18" customWidth="1"/>
-    <col min="10" max="11" width="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.3046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.07421875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.53515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.3046875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="22" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="21.07421875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20.53515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="22.15234375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.765625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.61328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="14.3046875" customWidth="1"/>
+    <col min="13" max="13" width="22" customWidth="1"/>
+    <col min="14" max="14" width="21.07421875" customWidth="1"/>
+    <col min="15" max="15" width="20.53515625" customWidth="1"/>
+    <col min="16" max="16" width="10" customWidth="1"/>
+    <col min="17" max="17" width="14.3046875" customWidth="1"/>
+    <col min="18" max="18" width="22" customWidth="1"/>
+    <col min="19" max="19" width="21.07421875" customWidth="1"/>
+    <col min="20" max="20" width="20.53515625" customWidth="1"/>
+    <col min="21" max="21" width="22.15234375" customWidth="1"/>
+    <col min="22" max="22" width="14.765625" customWidth="1"/>
+    <col min="23" max="23" width="3.61328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="42" customHeight="1" x14ac:dyDescent="0.45">
@@ -42268,57 +44354,57 @@
         <v>1169</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1226</v>
+        <v>1170</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1" t="s">
-        <v>1225</v>
+        <v>1177</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1227</v>
+        <v>1178</v>
       </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1" t="s">
-        <v>1219</v>
+        <v>1179</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>1220</v>
+        <v>1181</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>1221</v>
+        <v>1182</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>1222</v>
+        <v>1183</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>1223</v>
+        <v>1184</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>1224</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="18" x14ac:dyDescent="0.45">
@@ -42370,7 +44456,7 @@
         <v>6</v>
       </c>
       <c r="M2" s="23">
-        <f xml:space="preserve"> 1406/885</f>
+        <f>1406/885</f>
         <v>1.5887005649717514</v>
       </c>
       <c r="N2" s="23">
@@ -42477,7 +44563,7 @@
         <v>0.3198666296193387</v>
       </c>
       <c r="U3" s="10">
-        <f t="shared" ref="U2:U33" si="7">S3+T3</f>
+        <f t="shared" ref="U3:U33" si="7">S3+T3</f>
         <v>1.90856719459109</v>
       </c>
       <c r="V3" s="18" t="str">
@@ -47546,7 +49632,7 @@
         <v>Наблюдение</v>
       </c>
     </row>
-    <row r="61" spans="1:41" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:41" ht="18" x14ac:dyDescent="0.45">
       <c r="A61" s="22"/>
       <c r="P61" s="13">
         <v>60</v>
@@ -47579,7 +49665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:41" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:41" ht="18" x14ac:dyDescent="0.45">
       <c r="P62" s="2">
         <v>61</v>
       </c>
@@ -47608,7 +49694,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:41" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:41" ht="18" x14ac:dyDescent="0.45">
       <c r="P63" s="2">
         <v>62</v>
       </c>
@@ -47634,7 +49720,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="64" spans="1:41" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:41" ht="18" x14ac:dyDescent="0.45">
       <c r="P64" s="2">
         <v>63</v>
       </c>
@@ -47660,7 +49746,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="65" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="65" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P65" s="2">
         <v>64</v>
       </c>
@@ -47686,7 +49772,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="66" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="66" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P66" s="2">
         <v>65</v>
       </c>
@@ -47712,7 +49798,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="67" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="67" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P67" s="2">
         <v>66</v>
       </c>
@@ -47738,7 +49824,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="68" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="68" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P68" s="2">
         <v>67</v>
       </c>
@@ -47764,7 +49850,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="69" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="69" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P69" s="2">
         <v>68</v>
       </c>
@@ -47790,7 +49876,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="70" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="70" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P70" s="2">
         <v>69</v>
       </c>
@@ -47816,7 +49902,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="71" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P71" s="2">
         <v>70</v>
       </c>
@@ -47842,7 +49928,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="72" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="72" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P72" s="2">
         <v>71</v>
       </c>
@@ -47868,7 +49954,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="73" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="73" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P73" s="2">
         <v>72</v>
       </c>
@@ -47894,7 +49980,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="74" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="74" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P74" s="2">
         <v>73</v>
       </c>
@@ -47920,7 +50006,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="75" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="75" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P75" s="2">
         <v>74</v>
       </c>
@@ -47946,7 +50032,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="76" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="76" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P76" s="2">
         <v>75</v>
       </c>
@@ -47972,7 +50058,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="77" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="77" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P77" s="2">
         <v>76</v>
       </c>
@@ -47998,7 +50084,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="78" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="78" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P78" s="2">
         <v>77</v>
       </c>
@@ -48024,7 +50110,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="79" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="79" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P79" s="2">
         <v>78</v>
       </c>
@@ -48050,7 +50136,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="80" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="80" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P80" s="2">
         <v>79</v>
       </c>
@@ -48076,7 +50162,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="81" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="81" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P81" s="2">
         <v>80</v>
       </c>
@@ -48102,7 +50188,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="82" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="82" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P82" s="2">
         <v>81</v>
       </c>
@@ -48128,7 +50214,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="83" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="83" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P83" s="2">
         <v>82</v>
       </c>
@@ -48154,7 +50240,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="84" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="84" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P84" s="2">
         <v>83</v>
       </c>
@@ -48180,7 +50266,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="85" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="85" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P85" s="2">
         <v>84</v>
       </c>
@@ -48206,7 +50292,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="86" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="86" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P86" s="2">
         <v>85</v>
       </c>
@@ -48232,7 +50318,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="87" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="87" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P87" s="2">
         <v>86</v>
       </c>
@@ -48258,7 +50344,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="88" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="88" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P88" s="2">
         <v>87</v>
       </c>
@@ -48284,7 +50370,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="89" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="89" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P89" s="2">
         <v>88</v>
       </c>
@@ -48310,7 +50396,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="90" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="90" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P90" s="2">
         <v>89</v>
       </c>
@@ -48336,7 +50422,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="91" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="91" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P91" s="2">
         <v>90</v>
       </c>
@@ -48362,7 +50448,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="92" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="92" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P92" s="2">
         <v>91</v>
       </c>
@@ -48388,7 +50474,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="93" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="93" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P93" s="2">
         <v>92</v>
       </c>
@@ -48414,7 +50500,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="94" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="94" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P94" s="2">
         <v>93</v>
       </c>
@@ -48440,7 +50526,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="95" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="95" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P95" s="2">
         <v>94</v>
       </c>
@@ -48466,7 +50552,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="96" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="96" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P96" s="2">
         <v>95</v>
       </c>
@@ -48492,7 +50578,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="97" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="97" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P97" s="2">
         <v>96</v>
       </c>
@@ -48518,7 +50604,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="98" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="98" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P98" s="2">
         <v>97</v>
       </c>
@@ -48544,7 +50630,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="99" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="99" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P99" s="2">
         <v>98</v>
       </c>
@@ -48570,7 +50656,7 @@
         <v>Упреждение</v>
       </c>
     </row>
-    <row r="100" spans="16:22" ht="18.45" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="100" spans="16:22" ht="18" x14ac:dyDescent="0.45">
       <c r="P100" s="2">
         <v>99</v>
       </c>
@@ -48598,8 +50684,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -48615,64 +50700,64 @@
   <sheetData>
     <row r="1" spans="1:20" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
-        <v>1176</v>
+        <v>1186</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>1178</v>
+        <v>1187</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>1179</v>
+        <v>1188</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>1180</v>
+        <v>1189</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>1181</v>
+        <v>1190</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>1182</v>
+        <v>1191</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>1183</v>
+        <v>1192</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>1184</v>
+        <v>1193</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>1185</v>
+        <v>1194</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>1186</v>
+        <v>1195</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>1187</v>
+        <v>1196</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>1188</v>
+        <v>1197</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>1189</v>
+        <v>1198</v>
       </c>
       <c r="O1" s="5" t="s">
         <v>1168</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>1190</v>
+        <v>1199</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>1191</v>
+        <v>1200</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>1192</v>
+        <v>1201</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>1193</v>
+        <v>1202</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>1194</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.4">
@@ -53615,15 +55700,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
-        <v>1195</v>
+        <v>1204</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1196</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>1197</v>
+        <v>1206</v>
       </c>
       <c r="B2">
         <v>60</v>
@@ -53631,7 +55716,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>1198</v>
+        <v>1207</v>
       </c>
       <c r="B3" s="8">
         <v>39</v>
@@ -53639,7 +55724,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>1199</v>
+        <v>1208</v>
       </c>
       <c r="B4" s="9">
         <v>0.96</v>
@@ -53647,7 +55732,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>1200</v>
+        <v>1209</v>
       </c>
       <c r="B5" s="8">
         <f>SLOPE('Прогноз 60 39'!C2:C61,'Прогноз 60 39'!A2:A61)</f>
@@ -53656,7 +55741,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>1201</v>
+        <v>1210</v>
       </c>
       <c r="B6" s="8">
         <f>INTERCEPT('Прогноз 60 39'!C2:C61,'Прогноз 60 39'!A2:A61)</f>
@@ -53665,7 +55750,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>1202</v>
+        <v>1211</v>
       </c>
       <c r="B7" s="8">
         <f>SUM('Фостер Стюарт'!E2:E60)</f>
@@ -53674,7 +55759,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="B8" s="8">
         <f>SUM('Фостер Стюарт'!F2:F60)</f>
@@ -53683,7 +55768,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="B9" s="8">
         <f>B7-B8</f>
@@ -53692,7 +55777,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>1205</v>
+        <v>1214</v>
       </c>
       <c r="B10" s="8">
         <f>SQRT(2*SUM('Фостер Стюарт'!H2:H60))</f>
@@ -53701,7 +55786,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>1206</v>
+        <v>1215</v>
       </c>
       <c r="B11" s="8">
         <f>B9/B10</f>
@@ -53710,7 +55795,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>1207</v>
+        <v>1216</v>
       </c>
       <c r="B12" s="8">
         <f>_xlfn.NORM.S.INV((1+B4)/2)</f>
@@ -53719,7 +55804,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>1208</v>
+        <v>1217</v>
       </c>
       <c r="B13" s="8">
         <f>2*(1-_xlfn.NORM.S.DIST(ABS(B11),TRUE))</f>
@@ -53728,7 +55813,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>1209</v>
+        <v>1218</v>
       </c>
       <c r="B14" s="8" t="str">
         <f>IF(ABS(B11)&gt;B12,"Нулевая гипотеза отклонена: тренд есть","Нет оснований отвергнуть отсутствие тренда")</f>
@@ -53737,7 +55822,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>1210</v>
+        <v>1219</v>
       </c>
       <c r="B15" s="8">
         <f>SUM('Прогноз 60 39'!E62:E100)</f>
@@ -53746,7 +55831,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>1211</v>
+        <v>1220</v>
       </c>
       <c r="B16" s="8">
         <f>SUM('Прогноз 60 39'!D62:D100)</f>
@@ -53755,7 +55840,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>1212</v>
+        <v>1221</v>
       </c>
       <c r="B17" s="8">
         <f>AVERAGE('Прогноз 60 39'!O62:O100)</f>
@@ -53764,7 +55849,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>1213</v>
+        <v>1222</v>
       </c>
       <c r="B18" s="8">
         <f>SQRT(AVERAGE('Прогноз 60 39'!Q62:Q100))</f>
@@ -53773,7 +55858,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>1214</v>
+        <v>1223</v>
       </c>
       <c r="B19" s="8">
         <f>SUM('Прогноз 60 39'!O62:O100)/B16*100</f>
@@ -53782,7 +55867,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>1192</v>
+        <v>1201</v>
       </c>
       <c r="B20" s="8">
         <f>AVERAGE('Прогноз 60 39'!R62:R100)</f>
@@ -53791,7 +55876,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>1215</v>
+        <v>1224</v>
       </c>
       <c r="B21" s="8">
         <f>AVERAGE('Прогноз 60 39'!E62:E100)-AVERAGE('Прогноз 60 39'!D62:D100)</f>
@@ -53800,7 +55885,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>1216</v>
+        <v>1225</v>
       </c>
       <c r="B22" s="8">
         <f>('Прогноз 60 39'!C61-'Прогноз 60 39'!C2)/(B2-1)</f>
@@ -53809,7 +55894,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>1217</v>
+        <v>1226</v>
       </c>
       <c r="B23" s="8">
         <f>'Прогноз 60 39'!E62</f>
@@ -53818,7 +55903,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>1218</v>
+        <v>1227</v>
       </c>
       <c r="B24" s="8">
         <f>'Прогноз 60 39'!E100</f>
@@ -53828,4 +55913,3099 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:M100"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="3" customWidth="1"/>
+    <col min="12" max="12" width="34" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="26" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="46" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="26" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>1234</v>
+      </c>
+      <c r="I1" s="26" t="s">
+        <v>1168</v>
+      </c>
+      <c r="J1" s="26" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="26.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="27">
+        <v>1</v>
+      </c>
+      <c r="B2" s="28">
+        <f>Лист2!A2</f>
+        <v>45537</v>
+      </c>
+      <c r="C2" s="29">
+        <f>Лист2!B2</f>
+        <v>1</v>
+      </c>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="L2" s="25" t="s">
+        <v>1204</v>
+      </c>
+      <c r="M2" s="25" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A3" s="27">
+        <v>2</v>
+      </c>
+      <c r="B3" s="28">
+        <f>Лист2!A3</f>
+        <v>45544</v>
+      </c>
+      <c r="C3" s="29">
+        <f>Лист2!B3</f>
+        <v>2</v>
+      </c>
+      <c r="D3" s="29">
+        <f t="shared" ref="D3:D34" si="0">C3-C2</f>
+        <v>1</v>
+      </c>
+      <c r="E3" s="30">
+        <f t="shared" ref="E3:E34" si="1">$M$6</f>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F3" s="30"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="L3" s="27" t="s">
+        <v>1235</v>
+      </c>
+      <c r="M3" s="27">
+        <f>COUNT(C2:C61)</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A4" s="27">
+        <v>3</v>
+      </c>
+      <c r="B4" s="28">
+        <f>Лист2!A4</f>
+        <v>45551</v>
+      </c>
+      <c r="C4" s="29">
+        <f>Лист2!B4</f>
+        <v>3</v>
+      </c>
+      <c r="D4" s="29">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E4" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F4" s="30"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="L4" s="27" t="s">
+        <v>1236</v>
+      </c>
+      <c r="M4" s="27">
+        <f>C2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A5" s="27">
+        <v>4</v>
+      </c>
+      <c r="B5" s="28">
+        <f>Лист2!A5</f>
+        <v>45565</v>
+      </c>
+      <c r="C5" s="29">
+        <f>Лист2!B5</f>
+        <v>1</v>
+      </c>
+      <c r="D5" s="29">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="E5" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F5" s="30"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="L5" s="27" t="s">
+        <v>1237</v>
+      </c>
+      <c r="M5" s="27">
+        <f>C61</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A6" s="27">
+        <v>5</v>
+      </c>
+      <c r="B6" s="28">
+        <f>Лист2!A6</f>
+        <v>45572</v>
+      </c>
+      <c r="C6" s="29">
+        <f>Лист2!B6</f>
+        <v>5</v>
+      </c>
+      <c r="D6" s="29">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E6" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F6" s="30"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="L6" s="27" t="s">
+        <v>1238</v>
+      </c>
+      <c r="M6" s="30">
+        <f>(M5-M4)/(M3-1)</f>
+        <v>1.6949152542372881E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A7" s="27">
+        <v>6</v>
+      </c>
+      <c r="B7" s="28">
+        <f>Лист2!A7</f>
+        <v>45579</v>
+      </c>
+      <c r="C7" s="29">
+        <f>Лист2!B7</f>
+        <v>5</v>
+      </c>
+      <c r="D7" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E7" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F7" s="30"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="L7" s="27" t="s">
+        <v>1239</v>
+      </c>
+      <c r="M7" s="30">
+        <f>STDEV(D3:D61)</f>
+        <v>3.2456417750350575</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A8" s="27">
+        <v>7</v>
+      </c>
+      <c r="B8" s="28">
+        <f>Лист2!A8</f>
+        <v>45586</v>
+      </c>
+      <c r="C8" s="29">
+        <f>Лист2!B8</f>
+        <v>2</v>
+      </c>
+      <c r="D8" s="29">
+        <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
+      <c r="E8" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F8" s="30"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="L8" s="27" t="s">
+        <v>1240</v>
+      </c>
+      <c r="M8" s="27">
+        <f>MIN(D3:D61)</f>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A9" s="27">
+        <v>8</v>
+      </c>
+      <c r="B9" s="28">
+        <f>Лист2!A9</f>
+        <v>45593</v>
+      </c>
+      <c r="C9" s="29">
+        <f>Лист2!B9</f>
+        <v>2</v>
+      </c>
+      <c r="D9" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E9" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F9" s="30"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="L9" s="27" t="s">
+        <v>1241</v>
+      </c>
+      <c r="M9" s="27">
+        <f>MAX(D3:D61)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A10" s="27">
+        <v>9</v>
+      </c>
+      <c r="B10" s="28">
+        <f>Лист2!A10</f>
+        <v>45600</v>
+      </c>
+      <c r="C10" s="29">
+        <f>Лист2!B10</f>
+        <v>3</v>
+      </c>
+      <c r="D10" s="29">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E10" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F10" s="30"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="L10" s="27" t="s">
+        <v>1242</v>
+      </c>
+      <c r="M10" s="31">
+        <f>F62</f>
+        <v>2.0169491525423728</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A11" s="27">
+        <v>10</v>
+      </c>
+      <c r="B11" s="28">
+        <f>Лист2!A11</f>
+        <v>45607</v>
+      </c>
+      <c r="C11" s="29">
+        <f>Лист2!B11</f>
+        <v>5</v>
+      </c>
+      <c r="D11" s="29">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E11" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F11" s="30"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="L11" s="27" t="s">
+        <v>1243</v>
+      </c>
+      <c r="M11" s="31">
+        <f>F100</f>
+        <v>2.6610169491525424</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A12" s="27">
+        <v>11</v>
+      </c>
+      <c r="B12" s="28">
+        <f>Лист2!A12</f>
+        <v>45614</v>
+      </c>
+      <c r="C12" s="29">
+        <f>Лист2!B12</f>
+        <v>4</v>
+      </c>
+      <c r="D12" s="29">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="E12" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F12" s="30"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="L12" s="27" t="s">
+        <v>1244</v>
+      </c>
+      <c r="M12" s="31">
+        <f>AVERAGE(I62:I100)</f>
+        <v>14.512820512820513</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A13" s="27">
+        <v>12</v>
+      </c>
+      <c r="B13" s="28">
+        <f>Лист2!A13</f>
+        <v>45621</v>
+      </c>
+      <c r="C13" s="29">
+        <f>Лист2!B13</f>
+        <v>4</v>
+      </c>
+      <c r="D13" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E13" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F13" s="30"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="L13" s="27" t="s">
+        <v>1245</v>
+      </c>
+      <c r="M13" s="31">
+        <f>SUM(I62:I100)/SUM(H62:H100)*100</f>
+        <v>86.544342507645254</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A14" s="27">
+        <v>13</v>
+      </c>
+      <c r="B14" s="28">
+        <f>Лист2!A14</f>
+        <v>45635</v>
+      </c>
+      <c r="C14" s="29">
+        <f>Лист2!B14</f>
+        <v>2</v>
+      </c>
+      <c r="D14" s="29">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="E14" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F14" s="30"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="L14" s="27" t="s">
+        <v>1246</v>
+      </c>
+      <c r="M14" s="31">
+        <f>AVERAGE(C2:C21)</f>
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A15" s="27">
+        <v>14</v>
+      </c>
+      <c r="B15" s="28">
+        <f>Лист2!A15</f>
+        <v>45642</v>
+      </c>
+      <c r="C15" s="29">
+        <f>Лист2!B15</f>
+        <v>4</v>
+      </c>
+      <c r="D15" s="29">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E15" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F15" s="30"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="L15" s="27" t="s">
+        <v>1247</v>
+      </c>
+      <c r="M15" s="31">
+        <f>AVERAGE(C22:C41)</f>
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A16" s="27">
+        <v>15</v>
+      </c>
+      <c r="B16" s="28">
+        <f>Лист2!A16</f>
+        <v>45649</v>
+      </c>
+      <c r="C16" s="29">
+        <f>Лист2!B16</f>
+        <v>2</v>
+      </c>
+      <c r="D16" s="29">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="E16" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F16" s="30"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="L16" s="27" t="s">
+        <v>1248</v>
+      </c>
+      <c r="M16" s="31">
+        <f>AVERAGE(C42:C61)</f>
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A17" s="27">
+        <v>16</v>
+      </c>
+      <c r="B17" s="28">
+        <f>Лист2!A17</f>
+        <v>45656</v>
+      </c>
+      <c r="C17" s="29">
+        <f>Лист2!B17</f>
+        <v>5</v>
+      </c>
+      <c r="D17" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E17" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F17" s="30"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A18" s="27">
+        <v>17</v>
+      </c>
+      <c r="B18" s="28">
+        <f>Лист2!A18</f>
+        <v>45663</v>
+      </c>
+      <c r="C18" s="29">
+        <f>Лист2!B18</f>
+        <v>2</v>
+      </c>
+      <c r="D18" s="29">
+        <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
+      <c r="E18" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F18" s="30"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
+      <c r="L18" s="32" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A19" s="27">
+        <v>18</v>
+      </c>
+      <c r="B19" s="28">
+        <f>Лист2!A19</f>
+        <v>45670</v>
+      </c>
+      <c r="C19" s="29">
+        <f>Лист2!B19</f>
+        <v>4</v>
+      </c>
+      <c r="D19" s="29">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E19" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F19" s="30"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="L19" s="32" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A20" s="27">
+        <v>19</v>
+      </c>
+      <c r="B20" s="28">
+        <f>Лист2!A20</f>
+        <v>45677</v>
+      </c>
+      <c r="C20" s="29">
+        <f>Лист2!B20</f>
+        <v>3</v>
+      </c>
+      <c r="D20" s="29">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="E20" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F20" s="30"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="L20" s="33" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A21" s="27">
+        <v>20</v>
+      </c>
+      <c r="B21" s="28">
+        <f>Лист2!A21</f>
+        <v>45684</v>
+      </c>
+      <c r="C21" s="29">
+        <f>Лист2!B21</f>
+        <v>4</v>
+      </c>
+      <c r="D21" s="29">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E21" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F21" s="30"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A22" s="27">
+        <v>21</v>
+      </c>
+      <c r="B22" s="28">
+        <f>Лист2!A22</f>
+        <v>45691</v>
+      </c>
+      <c r="C22" s="29">
+        <f>Лист2!B22</f>
+        <v>1</v>
+      </c>
+      <c r="D22" s="29">
+        <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
+      <c r="E22" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F22" s="30"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="27"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A23" s="27">
+        <v>22</v>
+      </c>
+      <c r="B23" s="28">
+        <f>Лист2!A23</f>
+        <v>45698</v>
+      </c>
+      <c r="C23" s="29">
+        <f>Лист2!B23</f>
+        <v>7</v>
+      </c>
+      <c r="D23" s="29">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E23" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F23" s="30"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A24" s="27">
+        <v>23</v>
+      </c>
+      <c r="B24" s="28">
+        <f>Лист2!A24</f>
+        <v>45712</v>
+      </c>
+      <c r="C24" s="29">
+        <f>Лист2!B24</f>
+        <v>8</v>
+      </c>
+      <c r="D24" s="29">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E24" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F24" s="30"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A25" s="27">
+        <v>24</v>
+      </c>
+      <c r="B25" s="28">
+        <f>Лист2!A25</f>
+        <v>45719</v>
+      </c>
+      <c r="C25" s="29">
+        <f>Лист2!B25</f>
+        <v>4</v>
+      </c>
+      <c r="D25" s="29">
+        <f t="shared" si="0"/>
+        <v>-4</v>
+      </c>
+      <c r="E25" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F25" s="30"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="27"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A26" s="27">
+        <v>25</v>
+      </c>
+      <c r="B26" s="28">
+        <f>Лист2!A26</f>
+        <v>45726</v>
+      </c>
+      <c r="C26" s="29">
+        <f>Лист2!B26</f>
+        <v>4</v>
+      </c>
+      <c r="D26" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E26" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F26" s="30"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="27"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A27" s="27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="28">
+        <f>Лист2!A27</f>
+        <v>45733</v>
+      </c>
+      <c r="C27" s="29">
+        <f>Лист2!B27</f>
+        <v>8</v>
+      </c>
+      <c r="D27" s="29">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E27" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F27" s="30"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A28" s="27">
+        <v>27</v>
+      </c>
+      <c r="B28" s="28">
+        <f>Лист2!A28</f>
+        <v>45740</v>
+      </c>
+      <c r="C28" s="29">
+        <f>Лист2!B28</f>
+        <v>5</v>
+      </c>
+      <c r="D28" s="29">
+        <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
+      <c r="E28" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F28" s="30"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A29" s="27">
+        <v>28</v>
+      </c>
+      <c r="B29" s="28">
+        <f>Лист2!A29</f>
+        <v>45747</v>
+      </c>
+      <c r="C29" s="29">
+        <f>Лист2!B29</f>
+        <v>8</v>
+      </c>
+      <c r="D29" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E29" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F29" s="30"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="27"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A30" s="27">
+        <v>29</v>
+      </c>
+      <c r="B30" s="28">
+        <f>Лист2!A30</f>
+        <v>45754</v>
+      </c>
+      <c r="C30" s="29">
+        <f>Лист2!B30</f>
+        <v>7</v>
+      </c>
+      <c r="D30" s="29">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="E30" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F30" s="30"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A31" s="27">
+        <v>30</v>
+      </c>
+      <c r="B31" s="28">
+        <f>Лист2!A31</f>
+        <v>45761</v>
+      </c>
+      <c r="C31" s="29">
+        <f>Лист2!B31</f>
+        <v>2</v>
+      </c>
+      <c r="D31" s="29">
+        <f t="shared" si="0"/>
+        <v>-5</v>
+      </c>
+      <c r="E31" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F31" s="30"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="27"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A32" s="27">
+        <v>31</v>
+      </c>
+      <c r="B32" s="28">
+        <f>Лист2!A32</f>
+        <v>45768</v>
+      </c>
+      <c r="C32" s="29">
+        <f>Лист2!B32</f>
+        <v>7</v>
+      </c>
+      <c r="D32" s="29">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E32" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F32" s="30"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="27"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A33" s="27">
+        <v>32</v>
+      </c>
+      <c r="B33" s="28">
+        <f>Лист2!A33</f>
+        <v>45775</v>
+      </c>
+      <c r="C33" s="29">
+        <f>Лист2!B33</f>
+        <v>9</v>
+      </c>
+      <c r="D33" s="29">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E33" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F33" s="30"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="27"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A34" s="27">
+        <v>33</v>
+      </c>
+      <c r="B34" s="28">
+        <f>Лист2!A34</f>
+        <v>45782</v>
+      </c>
+      <c r="C34" s="29">
+        <f>Лист2!B34</f>
+        <v>6</v>
+      </c>
+      <c r="D34" s="29">
+        <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
+      <c r="E34" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F34" s="30"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="27"/>
+      <c r="J34" s="27"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A35" s="27">
+        <v>34</v>
+      </c>
+      <c r="B35" s="28">
+        <f>Лист2!A35</f>
+        <v>45789</v>
+      </c>
+      <c r="C35" s="29">
+        <f>Лист2!B35</f>
+        <v>8</v>
+      </c>
+      <c r="D35" s="29">
+        <f t="shared" ref="D35:D61" si="2">C35-C34</f>
+        <v>2</v>
+      </c>
+      <c r="E35" s="30">
+        <f t="shared" ref="E35:E66" si="3">$M$6</f>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F35" s="30"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="27"/>
+      <c r="J35" s="27"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A36" s="27">
+        <v>35</v>
+      </c>
+      <c r="B36" s="28">
+        <f>Лист2!A36</f>
+        <v>45796</v>
+      </c>
+      <c r="C36" s="29">
+        <f>Лист2!B36</f>
+        <v>5</v>
+      </c>
+      <c r="D36" s="29">
+        <f t="shared" si="2"/>
+        <v>-3</v>
+      </c>
+      <c r="E36" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F36" s="30"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="27"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A37" s="27">
+        <v>36</v>
+      </c>
+      <c r="B37" s="28">
+        <f>Лист2!A37</f>
+        <v>45803</v>
+      </c>
+      <c r="C37" s="29">
+        <f>Лист2!B37</f>
+        <v>10</v>
+      </c>
+      <c r="D37" s="29">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="E37" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F37" s="30"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="27"/>
+      <c r="J37" s="27"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A38" s="27">
+        <v>37</v>
+      </c>
+      <c r="B38" s="28">
+        <f>Лист2!A38</f>
+        <v>45810</v>
+      </c>
+      <c r="C38" s="29">
+        <f>Лист2!B38</f>
+        <v>8</v>
+      </c>
+      <c r="D38" s="29">
+        <f t="shared" si="2"/>
+        <v>-2</v>
+      </c>
+      <c r="E38" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F38" s="30"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="27"/>
+      <c r="J38" s="27"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A39" s="27">
+        <v>38</v>
+      </c>
+      <c r="B39" s="28">
+        <f>Лист2!A39</f>
+        <v>45817</v>
+      </c>
+      <c r="C39" s="29">
+        <f>Лист2!B39</f>
+        <v>9</v>
+      </c>
+      <c r="D39" s="29">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E39" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F39" s="30"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="27"/>
+      <c r="J39" s="27"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A40" s="27">
+        <v>39</v>
+      </c>
+      <c r="B40" s="28">
+        <f>Лист2!A40</f>
+        <v>45824</v>
+      </c>
+      <c r="C40" s="29">
+        <f>Лист2!B40</f>
+        <v>8</v>
+      </c>
+      <c r="D40" s="29">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="E40" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F40" s="30"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
+      <c r="J40" s="27"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A41" s="27">
+        <v>40</v>
+      </c>
+      <c r="B41" s="28">
+        <f>Лист2!A41</f>
+        <v>45831</v>
+      </c>
+      <c r="C41" s="29">
+        <f>Лист2!B41</f>
+        <v>7</v>
+      </c>
+      <c r="D41" s="29">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="E41" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F41" s="30"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="27"/>
+      <c r="J41" s="27"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A42" s="27">
+        <v>41</v>
+      </c>
+      <c r="B42" s="28">
+        <f>Лист2!A42</f>
+        <v>45838</v>
+      </c>
+      <c r="C42" s="29">
+        <f>Лист2!B42</f>
+        <v>10</v>
+      </c>
+      <c r="D42" s="29">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="E42" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F42" s="30"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="27"/>
+      <c r="J42" s="27"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A43" s="27">
+        <v>42</v>
+      </c>
+      <c r="B43" s="28">
+        <f>Лист2!A43</f>
+        <v>45845</v>
+      </c>
+      <c r="C43" s="29">
+        <f>Лист2!B43</f>
+        <v>7</v>
+      </c>
+      <c r="D43" s="29">
+        <f t="shared" si="2"/>
+        <v>-3</v>
+      </c>
+      <c r="E43" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F43" s="30"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="27"/>
+      <c r="J43" s="27"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A44" s="27">
+        <v>43</v>
+      </c>
+      <c r="B44" s="28">
+        <f>Лист2!A44</f>
+        <v>45852</v>
+      </c>
+      <c r="C44" s="29">
+        <f>Лист2!B44</f>
+        <v>4</v>
+      </c>
+      <c r="D44" s="29">
+        <f t="shared" si="2"/>
+        <v>-3</v>
+      </c>
+      <c r="E44" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F44" s="30"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="27"/>
+      <c r="I44" s="27"/>
+      <c r="J44" s="27"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A45" s="27">
+        <v>44</v>
+      </c>
+      <c r="B45" s="28">
+        <f>Лист2!A45</f>
+        <v>45859</v>
+      </c>
+      <c r="C45" s="29">
+        <f>Лист2!B45</f>
+        <v>7</v>
+      </c>
+      <c r="D45" s="29">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="E45" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F45" s="30"/>
+      <c r="G45" s="27"/>
+      <c r="H45" s="27"/>
+      <c r="I45" s="27"/>
+      <c r="J45" s="27"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A46" s="27">
+        <v>45</v>
+      </c>
+      <c r="B46" s="28">
+        <f>Лист2!A46</f>
+        <v>45866</v>
+      </c>
+      <c r="C46" s="29">
+        <f>Лист2!B46</f>
+        <v>9</v>
+      </c>
+      <c r="D46" s="29">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="E46" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F46" s="30"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
+      <c r="I46" s="27"/>
+      <c r="J46" s="27"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A47" s="27">
+        <v>46</v>
+      </c>
+      <c r="B47" s="28">
+        <f>Лист2!A47</f>
+        <v>45873</v>
+      </c>
+      <c r="C47" s="29">
+        <f>Лист2!B47</f>
+        <v>8</v>
+      </c>
+      <c r="D47" s="29">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="E47" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F47" s="30"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="27"/>
+      <c r="I47" s="27"/>
+      <c r="J47" s="27"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A48" s="27">
+        <v>47</v>
+      </c>
+      <c r="B48" s="28">
+        <f>Лист2!A48</f>
+        <v>45880</v>
+      </c>
+      <c r="C48" s="29">
+        <f>Лист2!B48</f>
+        <v>9</v>
+      </c>
+      <c r="D48" s="29">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E48" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F48" s="30"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="27"/>
+      <c r="I48" s="27"/>
+      <c r="J48" s="27"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A49" s="27">
+        <v>48</v>
+      </c>
+      <c r="B49" s="28">
+        <f>Лист2!A49</f>
+        <v>45887</v>
+      </c>
+      <c r="C49" s="29">
+        <f>Лист2!B49</f>
+        <v>14</v>
+      </c>
+      <c r="D49" s="29">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="E49" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F49" s="30"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="27"/>
+      <c r="I49" s="27"/>
+      <c r="J49" s="27"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A50" s="27">
+        <v>49</v>
+      </c>
+      <c r="B50" s="28">
+        <f>Лист2!A50</f>
+        <v>45894</v>
+      </c>
+      <c r="C50" s="29">
+        <f>Лист2!B50</f>
+        <v>9</v>
+      </c>
+      <c r="D50" s="29">
+        <f t="shared" si="2"/>
+        <v>-5</v>
+      </c>
+      <c r="E50" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F50" s="30"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="27"/>
+      <c r="I50" s="27"/>
+      <c r="J50" s="27"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A51" s="27">
+        <v>50</v>
+      </c>
+      <c r="B51" s="28">
+        <f>Лист2!A51</f>
+        <v>45901</v>
+      </c>
+      <c r="C51" s="29">
+        <f>Лист2!B51</f>
+        <v>12</v>
+      </c>
+      <c r="D51" s="29">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="E51" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F51" s="30"/>
+      <c r="G51" s="27"/>
+      <c r="H51" s="27"/>
+      <c r="I51" s="27"/>
+      <c r="J51" s="27"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A52" s="27">
+        <v>51</v>
+      </c>
+      <c r="B52" s="28">
+        <f>Лист2!A52</f>
+        <v>45908</v>
+      </c>
+      <c r="C52" s="29">
+        <f>Лист2!B52</f>
+        <v>9</v>
+      </c>
+      <c r="D52" s="29">
+        <f t="shared" si="2"/>
+        <v>-3</v>
+      </c>
+      <c r="E52" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F52" s="30"/>
+      <c r="G52" s="27"/>
+      <c r="H52" s="27"/>
+      <c r="I52" s="27"/>
+      <c r="J52" s="27"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A53" s="27">
+        <v>52</v>
+      </c>
+      <c r="B53" s="28">
+        <f>Лист2!A53</f>
+        <v>45915</v>
+      </c>
+      <c r="C53" s="29">
+        <f>Лист2!B53</f>
+        <v>11</v>
+      </c>
+      <c r="D53" s="29">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="E53" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F53" s="30"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="27"/>
+      <c r="I53" s="27"/>
+      <c r="J53" s="27"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A54" s="27">
+        <v>53</v>
+      </c>
+      <c r="B54" s="28">
+        <f>Лист2!A54</f>
+        <v>45922</v>
+      </c>
+      <c r="C54" s="29">
+        <f>Лист2!B54</f>
+        <v>15</v>
+      </c>
+      <c r="D54" s="29">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="E54" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F54" s="30"/>
+      <c r="G54" s="27"/>
+      <c r="H54" s="27"/>
+      <c r="I54" s="27"/>
+      <c r="J54" s="27"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A55" s="27">
+        <v>54</v>
+      </c>
+      <c r="B55" s="28">
+        <f>Лист2!A55</f>
+        <v>45929</v>
+      </c>
+      <c r="C55" s="29">
+        <f>Лист2!B55</f>
+        <v>8</v>
+      </c>
+      <c r="D55" s="29">
+        <f t="shared" si="2"/>
+        <v>-7</v>
+      </c>
+      <c r="E55" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F55" s="30"/>
+      <c r="G55" s="27"/>
+      <c r="H55" s="27"/>
+      <c r="I55" s="27"/>
+      <c r="J55" s="27"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A56" s="27">
+        <v>55</v>
+      </c>
+      <c r="B56" s="28">
+        <f>Лист2!A56</f>
+        <v>45936</v>
+      </c>
+      <c r="C56" s="29">
+        <f>Лист2!B56</f>
+        <v>14</v>
+      </c>
+      <c r="D56" s="29">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="E56" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F56" s="30"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="27"/>
+      <c r="I56" s="27"/>
+      <c r="J56" s="27"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A57" s="27">
+        <v>56</v>
+      </c>
+      <c r="B57" s="28">
+        <f>Лист2!A57</f>
+        <v>45943</v>
+      </c>
+      <c r="C57" s="29">
+        <f>Лист2!B57</f>
+        <v>15</v>
+      </c>
+      <c r="D57" s="29">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E57" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F57" s="30"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="27"/>
+      <c r="I57" s="27"/>
+      <c r="J57" s="27"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A58" s="27">
+        <v>57</v>
+      </c>
+      <c r="B58" s="28">
+        <f>Лист2!A58</f>
+        <v>45950</v>
+      </c>
+      <c r="C58" s="29">
+        <f>Лист2!B58</f>
+        <v>9</v>
+      </c>
+      <c r="D58" s="29">
+        <f t="shared" si="2"/>
+        <v>-6</v>
+      </c>
+      <c r="E58" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F58" s="30"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="27"/>
+      <c r="I58" s="27"/>
+      <c r="J58" s="27"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A59" s="27">
+        <v>58</v>
+      </c>
+      <c r="B59" s="28">
+        <f>Лист2!A59</f>
+        <v>45957</v>
+      </c>
+      <c r="C59" s="29">
+        <f>Лист2!B59</f>
+        <v>13</v>
+      </c>
+      <c r="D59" s="29">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="E59" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F59" s="30"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="27"/>
+      <c r="I59" s="27"/>
+      <c r="J59" s="27"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A60" s="27">
+        <v>59</v>
+      </c>
+      <c r="B60" s="28">
+        <f>Лист2!A60</f>
+        <v>45964</v>
+      </c>
+      <c r="C60" s="29">
+        <f>Лист2!B60</f>
+        <v>9</v>
+      </c>
+      <c r="D60" s="29">
+        <f t="shared" si="2"/>
+        <v>-4</v>
+      </c>
+      <c r="E60" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F60" s="30"/>
+      <c r="G60" s="27"/>
+      <c r="H60" s="27"/>
+      <c r="I60" s="27"/>
+      <c r="J60" s="27"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A61" s="34">
+        <v>60</v>
+      </c>
+      <c r="B61" s="35">
+        <f>Лист2!A61</f>
+        <v>45971</v>
+      </c>
+      <c r="C61" s="36">
+        <f>Лист2!B61</f>
+        <v>2</v>
+      </c>
+      <c r="D61" s="36">
+        <f t="shared" si="2"/>
+        <v>-7</v>
+      </c>
+      <c r="E61" s="37">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F61" s="37">
+        <f>C61</f>
+        <v>2</v>
+      </c>
+      <c r="G61" s="36">
+        <f>C61</f>
+        <v>2</v>
+      </c>
+      <c r="H61" s="36"/>
+      <c r="I61" s="36"/>
+      <c r="J61" s="34"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A62" s="27">
+        <v>61</v>
+      </c>
+      <c r="B62" s="28">
+        <f t="shared" ref="B62:B100" si="4">B61+7</f>
+        <v>45978</v>
+      </c>
+      <c r="C62" s="27"/>
+      <c r="D62" s="27"/>
+      <c r="E62" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F62" s="38">
+        <f t="shared" ref="F62:F100" si="5">$M$5+(A62-$M$3)*$M$6</f>
+        <v>2.0169491525423728</v>
+      </c>
+      <c r="G62" s="39">
+        <f t="shared" ref="G62:G100" si="6">ROUND(F62,0)</f>
+        <v>2</v>
+      </c>
+      <c r="H62" s="40">
+        <f>Лист2!B62</f>
+        <v>22</v>
+      </c>
+      <c r="I62" s="40">
+        <f t="shared" ref="I62:I100" si="7">ABS(H62-G62)</f>
+        <v>20</v>
+      </c>
+      <c r="J62" s="41">
+        <f t="shared" ref="J62:J100" si="8">IF(H62=0,"",I62/H62*100)</f>
+        <v>90.909090909090907</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A63" s="27">
+        <v>62</v>
+      </c>
+      <c r="B63" s="28">
+        <f t="shared" si="4"/>
+        <v>45985</v>
+      </c>
+      <c r="C63" s="27"/>
+      <c r="D63" s="27"/>
+      <c r="E63" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F63" s="38">
+        <f t="shared" si="5"/>
+        <v>2.0338983050847457</v>
+      </c>
+      <c r="G63" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H63" s="40">
+        <f>Лист2!B63</f>
+        <v>21</v>
+      </c>
+      <c r="I63" s="40">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="J63" s="41">
+        <f t="shared" si="8"/>
+        <v>90.476190476190482</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A64" s="27">
+        <v>63</v>
+      </c>
+      <c r="B64" s="28">
+        <f t="shared" si="4"/>
+        <v>45992</v>
+      </c>
+      <c r="C64" s="27"/>
+      <c r="D64" s="27"/>
+      <c r="E64" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F64" s="38">
+        <f t="shared" si="5"/>
+        <v>2.0508474576271185</v>
+      </c>
+      <c r="G64" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H64" s="40">
+        <f>Лист2!B64</f>
+        <v>19</v>
+      </c>
+      <c r="I64" s="40">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+      <c r="J64" s="41">
+        <f t="shared" si="8"/>
+        <v>89.473684210526315</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A65" s="27">
+        <v>64</v>
+      </c>
+      <c r="B65" s="28">
+        <f t="shared" si="4"/>
+        <v>45999</v>
+      </c>
+      <c r="C65" s="27"/>
+      <c r="D65" s="27"/>
+      <c r="E65" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F65" s="38">
+        <f t="shared" si="5"/>
+        <v>2.0677966101694913</v>
+      </c>
+      <c r="G65" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H65" s="40">
+        <f>Лист2!B65</f>
+        <v>21</v>
+      </c>
+      <c r="I65" s="40">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="J65" s="41">
+        <f t="shared" si="8"/>
+        <v>90.476190476190482</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A66" s="27">
+        <v>65</v>
+      </c>
+      <c r="B66" s="28">
+        <f t="shared" si="4"/>
+        <v>46006</v>
+      </c>
+      <c r="C66" s="27"/>
+      <c r="D66" s="27"/>
+      <c r="E66" s="30">
+        <f t="shared" si="3"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F66" s="38">
+        <f t="shared" si="5"/>
+        <v>2.0847457627118642</v>
+      </c>
+      <c r="G66" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H66" s="40">
+        <f>Лист2!B66</f>
+        <v>10</v>
+      </c>
+      <c r="I66" s="40">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="J66" s="41">
+        <f t="shared" si="8"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A67" s="27">
+        <v>66</v>
+      </c>
+      <c r="B67" s="28">
+        <f t="shared" si="4"/>
+        <v>46013</v>
+      </c>
+      <c r="C67" s="27"/>
+      <c r="D67" s="27"/>
+      <c r="E67" s="30">
+        <f t="shared" ref="E67:E100" si="9">$M$6</f>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F67" s="38">
+        <f t="shared" si="5"/>
+        <v>2.1016949152542375</v>
+      </c>
+      <c r="G67" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H67" s="40">
+        <f>Лист2!B67</f>
+        <v>7</v>
+      </c>
+      <c r="I67" s="40">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="J67" s="41">
+        <f t="shared" si="8"/>
+        <v>71.428571428571431</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A68" s="27">
+        <v>67</v>
+      </c>
+      <c r="B68" s="28">
+        <f t="shared" si="4"/>
+        <v>46020</v>
+      </c>
+      <c r="C68" s="27"/>
+      <c r="D68" s="27"/>
+      <c r="E68" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F68" s="38">
+        <f t="shared" si="5"/>
+        <v>2.1186440677966103</v>
+      </c>
+      <c r="G68" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H68" s="40">
+        <f>Лист2!B68</f>
+        <v>11</v>
+      </c>
+      <c r="I68" s="40">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="J68" s="41">
+        <f t="shared" si="8"/>
+        <v>81.818181818181827</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A69" s="27">
+        <v>68</v>
+      </c>
+      <c r="B69" s="28">
+        <f t="shared" si="4"/>
+        <v>46027</v>
+      </c>
+      <c r="C69" s="27"/>
+      <c r="D69" s="27"/>
+      <c r="E69" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F69" s="38">
+        <f t="shared" si="5"/>
+        <v>2.1355932203389831</v>
+      </c>
+      <c r="G69" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H69" s="40">
+        <f>Лист2!B69</f>
+        <v>21</v>
+      </c>
+      <c r="I69" s="40">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="J69" s="41">
+        <f t="shared" si="8"/>
+        <v>90.476190476190482</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A70" s="27">
+        <v>69</v>
+      </c>
+      <c r="B70" s="28">
+        <f t="shared" si="4"/>
+        <v>46034</v>
+      </c>
+      <c r="C70" s="27"/>
+      <c r="D70" s="27"/>
+      <c r="E70" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F70" s="38">
+        <f t="shared" si="5"/>
+        <v>2.152542372881356</v>
+      </c>
+      <c r="G70" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H70" s="40">
+        <f>Лист2!B70</f>
+        <v>15</v>
+      </c>
+      <c r="I70" s="40">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="J70" s="41">
+        <f t="shared" si="8"/>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A71" s="27">
+        <v>70</v>
+      </c>
+      <c r="B71" s="28">
+        <f t="shared" si="4"/>
+        <v>46041</v>
+      </c>
+      <c r="C71" s="27"/>
+      <c r="D71" s="27"/>
+      <c r="E71" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F71" s="38">
+        <f t="shared" si="5"/>
+        <v>2.1694915254237288</v>
+      </c>
+      <c r="G71" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H71" s="40">
+        <f>Лист2!B71</f>
+        <v>9</v>
+      </c>
+      <c r="I71" s="40">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="J71" s="41">
+        <f t="shared" si="8"/>
+        <v>77.777777777777786</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A72" s="27">
+        <v>71</v>
+      </c>
+      <c r="B72" s="28">
+        <f t="shared" si="4"/>
+        <v>46048</v>
+      </c>
+      <c r="C72" s="27"/>
+      <c r="D72" s="27"/>
+      <c r="E72" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F72" s="38">
+        <f t="shared" si="5"/>
+        <v>2.1864406779661016</v>
+      </c>
+      <c r="G72" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H72" s="40">
+        <f>Лист2!B72</f>
+        <v>10</v>
+      </c>
+      <c r="I72" s="40">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="J72" s="41">
+        <f t="shared" si="8"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A73" s="27">
+        <v>72</v>
+      </c>
+      <c r="B73" s="28">
+        <f t="shared" si="4"/>
+        <v>46055</v>
+      </c>
+      <c r="C73" s="27"/>
+      <c r="D73" s="27"/>
+      <c r="E73" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F73" s="38">
+        <f t="shared" si="5"/>
+        <v>2.2033898305084745</v>
+      </c>
+      <c r="G73" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H73" s="40">
+        <f>Лист2!B73</f>
+        <v>15</v>
+      </c>
+      <c r="I73" s="40">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="J73" s="41">
+        <f t="shared" si="8"/>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A74" s="27">
+        <v>73</v>
+      </c>
+      <c r="B74" s="28">
+        <f t="shared" si="4"/>
+        <v>46062</v>
+      </c>
+      <c r="C74" s="27"/>
+      <c r="D74" s="27"/>
+      <c r="E74" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F74" s="38">
+        <f t="shared" si="5"/>
+        <v>2.2203389830508473</v>
+      </c>
+      <c r="G74" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H74" s="40">
+        <f>Лист2!B74</f>
+        <v>20</v>
+      </c>
+      <c r="I74" s="40">
+        <f t="shared" si="7"/>
+        <v>18</v>
+      </c>
+      <c r="J74" s="41">
+        <f t="shared" si="8"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A75" s="27">
+        <v>74</v>
+      </c>
+      <c r="B75" s="28">
+        <f t="shared" si="4"/>
+        <v>46069</v>
+      </c>
+      <c r="C75" s="27"/>
+      <c r="D75" s="27"/>
+      <c r="E75" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F75" s="38">
+        <f t="shared" si="5"/>
+        <v>2.2372881355932202</v>
+      </c>
+      <c r="G75" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H75" s="40">
+        <f>Лист2!B75</f>
+        <v>15</v>
+      </c>
+      <c r="I75" s="40">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="J75" s="41">
+        <f t="shared" si="8"/>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A76" s="27">
+        <v>75</v>
+      </c>
+      <c r="B76" s="28">
+        <f t="shared" si="4"/>
+        <v>46076</v>
+      </c>
+      <c r="C76" s="27"/>
+      <c r="D76" s="27"/>
+      <c r="E76" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F76" s="38">
+        <f t="shared" si="5"/>
+        <v>2.2542372881355934</v>
+      </c>
+      <c r="G76" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H76" s="40">
+        <f>Лист2!B76</f>
+        <v>15</v>
+      </c>
+      <c r="I76" s="40">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="J76" s="41">
+        <f t="shared" si="8"/>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A77" s="27">
+        <v>76</v>
+      </c>
+      <c r="B77" s="28">
+        <f t="shared" si="4"/>
+        <v>46083</v>
+      </c>
+      <c r="C77" s="27"/>
+      <c r="D77" s="27"/>
+      <c r="E77" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F77" s="38">
+        <f t="shared" si="5"/>
+        <v>2.2711864406779663</v>
+      </c>
+      <c r="G77" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H77" s="40">
+        <f>Лист2!B77</f>
+        <v>16</v>
+      </c>
+      <c r="I77" s="40">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="J77" s="41">
+        <f t="shared" si="8"/>
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A78" s="27">
+        <v>77</v>
+      </c>
+      <c r="B78" s="28">
+        <f t="shared" si="4"/>
+        <v>46090</v>
+      </c>
+      <c r="C78" s="27"/>
+      <c r="D78" s="27"/>
+      <c r="E78" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F78" s="38">
+        <f t="shared" si="5"/>
+        <v>2.2881355932203391</v>
+      </c>
+      <c r="G78" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H78" s="40">
+        <f>Лист2!B78</f>
+        <v>14</v>
+      </c>
+      <c r="I78" s="40">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="J78" s="41">
+        <f t="shared" si="8"/>
+        <v>85.714285714285708</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A79" s="27">
+        <v>78</v>
+      </c>
+      <c r="B79" s="28">
+        <f t="shared" si="4"/>
+        <v>46097</v>
+      </c>
+      <c r="C79" s="27"/>
+      <c r="D79" s="27"/>
+      <c r="E79" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F79" s="38">
+        <f t="shared" si="5"/>
+        <v>2.3050847457627119</v>
+      </c>
+      <c r="G79" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H79" s="40">
+        <f>Лист2!B79</f>
+        <v>15</v>
+      </c>
+      <c r="I79" s="40">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="J79" s="41">
+        <f t="shared" si="8"/>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A80" s="27">
+        <v>79</v>
+      </c>
+      <c r="B80" s="28">
+        <f t="shared" si="4"/>
+        <v>46104</v>
+      </c>
+      <c r="C80" s="27"/>
+      <c r="D80" s="27"/>
+      <c r="E80" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F80" s="38">
+        <f t="shared" si="5"/>
+        <v>2.3220338983050848</v>
+      </c>
+      <c r="G80" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H80" s="40">
+        <f>Лист2!B80</f>
+        <v>30</v>
+      </c>
+      <c r="I80" s="40">
+        <f t="shared" si="7"/>
+        <v>28</v>
+      </c>
+      <c r="J80" s="41">
+        <f t="shared" si="8"/>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A81" s="27">
+        <v>80</v>
+      </c>
+      <c r="B81" s="28">
+        <f t="shared" si="4"/>
+        <v>46111</v>
+      </c>
+      <c r="C81" s="27"/>
+      <c r="D81" s="27"/>
+      <c r="E81" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F81" s="38">
+        <f t="shared" si="5"/>
+        <v>2.3389830508474576</v>
+      </c>
+      <c r="G81" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H81" s="40">
+        <f>Лист2!B81</f>
+        <v>17</v>
+      </c>
+      <c r="I81" s="40">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="J81" s="41">
+        <f t="shared" si="8"/>
+        <v>88.235294117647058</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A82" s="27">
+        <v>81</v>
+      </c>
+      <c r="B82" s="28">
+        <f t="shared" si="4"/>
+        <v>46118</v>
+      </c>
+      <c r="C82" s="27"/>
+      <c r="D82" s="27"/>
+      <c r="E82" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F82" s="38">
+        <f t="shared" si="5"/>
+        <v>2.3559322033898304</v>
+      </c>
+      <c r="G82" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H82" s="40">
+        <f>Лист2!B82</f>
+        <v>14</v>
+      </c>
+      <c r="I82" s="40">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="J82" s="41">
+        <f t="shared" si="8"/>
+        <v>85.714285714285708</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A83" s="27">
+        <v>82</v>
+      </c>
+      <c r="B83" s="28">
+        <f t="shared" si="4"/>
+        <v>46125</v>
+      </c>
+      <c r="C83" s="27"/>
+      <c r="D83" s="27"/>
+      <c r="E83" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F83" s="38">
+        <f t="shared" si="5"/>
+        <v>2.3728813559322033</v>
+      </c>
+      <c r="G83" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H83" s="40">
+        <f>Лист2!B83</f>
+        <v>11</v>
+      </c>
+      <c r="I83" s="40">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="J83" s="41">
+        <f t="shared" si="8"/>
+        <v>81.818181818181827</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A84" s="27">
+        <v>83</v>
+      </c>
+      <c r="B84" s="28">
+        <f t="shared" si="4"/>
+        <v>46132</v>
+      </c>
+      <c r="C84" s="27"/>
+      <c r="D84" s="27"/>
+      <c r="E84" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F84" s="38">
+        <f t="shared" si="5"/>
+        <v>2.3898305084745761</v>
+      </c>
+      <c r="G84" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H84" s="40">
+        <f>Лист2!B84</f>
+        <v>18</v>
+      </c>
+      <c r="I84" s="40">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="J84" s="41">
+        <f t="shared" si="8"/>
+        <v>88.888888888888886</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A85" s="27">
+        <v>84</v>
+      </c>
+      <c r="B85" s="28">
+        <f t="shared" si="4"/>
+        <v>46139</v>
+      </c>
+      <c r="C85" s="27"/>
+      <c r="D85" s="27"/>
+      <c r="E85" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F85" s="38">
+        <f t="shared" si="5"/>
+        <v>2.406779661016949</v>
+      </c>
+      <c r="G85" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H85" s="40">
+        <f>Лист2!B85</f>
+        <v>19</v>
+      </c>
+      <c r="I85" s="40">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+      <c r="J85" s="41">
+        <f t="shared" si="8"/>
+        <v>89.473684210526315</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A86" s="27">
+        <v>85</v>
+      </c>
+      <c r="B86" s="28">
+        <f t="shared" si="4"/>
+        <v>46146</v>
+      </c>
+      <c r="C86" s="27"/>
+      <c r="D86" s="27"/>
+      <c r="E86" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F86" s="38">
+        <f t="shared" si="5"/>
+        <v>2.4237288135593218</v>
+      </c>
+      <c r="G86" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H86" s="40">
+        <f>Лист2!B86</f>
+        <v>19</v>
+      </c>
+      <c r="I86" s="40">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+      <c r="J86" s="41">
+        <f t="shared" si="8"/>
+        <v>89.473684210526315</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A87" s="27">
+        <v>86</v>
+      </c>
+      <c r="B87" s="28">
+        <f t="shared" si="4"/>
+        <v>46153</v>
+      </c>
+      <c r="C87" s="27"/>
+      <c r="D87" s="27"/>
+      <c r="E87" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F87" s="38">
+        <f t="shared" si="5"/>
+        <v>2.4406779661016951</v>
+      </c>
+      <c r="G87" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H87" s="40">
+        <f>Лист2!B87</f>
+        <v>14</v>
+      </c>
+      <c r="I87" s="40">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="J87" s="41">
+        <f t="shared" si="8"/>
+        <v>85.714285714285708</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A88" s="27">
+        <v>87</v>
+      </c>
+      <c r="B88" s="28">
+        <f t="shared" si="4"/>
+        <v>46160</v>
+      </c>
+      <c r="C88" s="27"/>
+      <c r="D88" s="27"/>
+      <c r="E88" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F88" s="38">
+        <f t="shared" si="5"/>
+        <v>2.4576271186440679</v>
+      </c>
+      <c r="G88" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H88" s="40">
+        <f>Лист2!B88</f>
+        <v>30</v>
+      </c>
+      <c r="I88" s="40">
+        <f t="shared" si="7"/>
+        <v>28</v>
+      </c>
+      <c r="J88" s="41">
+        <f t="shared" si="8"/>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A89" s="27">
+        <v>88</v>
+      </c>
+      <c r="B89" s="28">
+        <f t="shared" si="4"/>
+        <v>46167</v>
+      </c>
+      <c r="C89" s="27"/>
+      <c r="D89" s="27"/>
+      <c r="E89" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F89" s="38">
+        <f t="shared" si="5"/>
+        <v>2.4745762711864407</v>
+      </c>
+      <c r="G89" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H89" s="40">
+        <f>Лист2!B89</f>
+        <v>9</v>
+      </c>
+      <c r="I89" s="40">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="J89" s="41">
+        <f t="shared" si="8"/>
+        <v>77.777777777777786</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A90" s="27">
+        <v>89</v>
+      </c>
+      <c r="B90" s="28">
+        <f t="shared" si="4"/>
+        <v>46174</v>
+      </c>
+      <c r="C90" s="27"/>
+      <c r="D90" s="27"/>
+      <c r="E90" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F90" s="38">
+        <f t="shared" si="5"/>
+        <v>2.4915254237288136</v>
+      </c>
+      <c r="G90" s="39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H90" s="40">
+        <f>Лист2!B90</f>
+        <v>31</v>
+      </c>
+      <c r="I90" s="40">
+        <f t="shared" si="7"/>
+        <v>29</v>
+      </c>
+      <c r="J90" s="41">
+        <f t="shared" si="8"/>
+        <v>93.548387096774192</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A91" s="27">
+        <v>90</v>
+      </c>
+      <c r="B91" s="28">
+        <f t="shared" si="4"/>
+        <v>46181</v>
+      </c>
+      <c r="C91" s="27"/>
+      <c r="D91" s="27"/>
+      <c r="E91" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F91" s="38">
+        <f t="shared" si="5"/>
+        <v>2.5084745762711864</v>
+      </c>
+      <c r="G91" s="39">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="H91" s="40">
+        <f>Лист2!B91</f>
+        <v>12</v>
+      </c>
+      <c r="I91" s="40">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="J91" s="41">
+        <f t="shared" si="8"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A92" s="27">
+        <v>91</v>
+      </c>
+      <c r="B92" s="28">
+        <f t="shared" si="4"/>
+        <v>46188</v>
+      </c>
+      <c r="C92" s="27"/>
+      <c r="D92" s="27"/>
+      <c r="E92" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F92" s="38">
+        <f t="shared" si="5"/>
+        <v>2.5254237288135593</v>
+      </c>
+      <c r="G92" s="39">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="H92" s="40">
+        <f>Лист2!B92</f>
+        <v>23</v>
+      </c>
+      <c r="I92" s="40">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="J92" s="41">
+        <f t="shared" si="8"/>
+        <v>86.956521739130437</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A93" s="27">
+        <v>92</v>
+      </c>
+      <c r="B93" s="28">
+        <f t="shared" si="4"/>
+        <v>46195</v>
+      </c>
+      <c r="C93" s="27"/>
+      <c r="D93" s="27"/>
+      <c r="E93" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F93" s="38">
+        <f t="shared" si="5"/>
+        <v>2.5423728813559321</v>
+      </c>
+      <c r="G93" s="39">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="H93" s="40">
+        <f>Лист2!B93</f>
+        <v>18</v>
+      </c>
+      <c r="I93" s="40">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="J93" s="41">
+        <f t="shared" si="8"/>
+        <v>83.333333333333343</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A94" s="27">
+        <v>93</v>
+      </c>
+      <c r="B94" s="28">
+        <f t="shared" si="4"/>
+        <v>46202</v>
+      </c>
+      <c r="C94" s="27"/>
+      <c r="D94" s="27"/>
+      <c r="E94" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F94" s="38">
+        <f t="shared" si="5"/>
+        <v>2.5593220338983049</v>
+      </c>
+      <c r="G94" s="39">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="H94" s="40">
+        <f>Лист2!B94</f>
+        <v>17</v>
+      </c>
+      <c r="I94" s="40">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="J94" s="41">
+        <f t="shared" si="8"/>
+        <v>82.35294117647058</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A95" s="27">
+        <v>94</v>
+      </c>
+      <c r="B95" s="28">
+        <f t="shared" si="4"/>
+        <v>46209</v>
+      </c>
+      <c r="C95" s="27"/>
+      <c r="D95" s="27"/>
+      <c r="E95" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F95" s="38">
+        <f t="shared" si="5"/>
+        <v>2.5762711864406782</v>
+      </c>
+      <c r="G95" s="39">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="H95" s="40">
+        <f>Лист2!B95</f>
+        <v>16</v>
+      </c>
+      <c r="I95" s="40">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="J95" s="41">
+        <f t="shared" si="8"/>
+        <v>81.25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A96" s="27">
+        <v>95</v>
+      </c>
+      <c r="B96" s="28">
+        <f t="shared" si="4"/>
+        <v>46216</v>
+      </c>
+      <c r="C96" s="27"/>
+      <c r="D96" s="27"/>
+      <c r="E96" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F96" s="38">
+        <f t="shared" si="5"/>
+        <v>2.593220338983051</v>
+      </c>
+      <c r="G96" s="39">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="H96" s="40">
+        <f>Лист2!B96</f>
+        <v>26</v>
+      </c>
+      <c r="I96" s="40">
+        <f t="shared" si="7"/>
+        <v>23</v>
+      </c>
+      <c r="J96" s="41">
+        <f t="shared" si="8"/>
+        <v>88.461538461538453</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A97" s="27">
+        <v>96</v>
+      </c>
+      <c r="B97" s="28">
+        <f t="shared" si="4"/>
+        <v>46223</v>
+      </c>
+      <c r="C97" s="27"/>
+      <c r="D97" s="27"/>
+      <c r="E97" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F97" s="38">
+        <f t="shared" si="5"/>
+        <v>2.6101694915254239</v>
+      </c>
+      <c r="G97" s="39">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="H97" s="40">
+        <f>Лист2!B97</f>
+        <v>12</v>
+      </c>
+      <c r="I97" s="40">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="J97" s="41">
+        <f t="shared" si="8"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A98" s="27">
+        <v>97</v>
+      </c>
+      <c r="B98" s="28">
+        <f t="shared" si="4"/>
+        <v>46230</v>
+      </c>
+      <c r="C98" s="27"/>
+      <c r="D98" s="27"/>
+      <c r="E98" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F98" s="38">
+        <f t="shared" si="5"/>
+        <v>2.6271186440677967</v>
+      </c>
+      <c r="G98" s="39">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="H98" s="40">
+        <f>Лист2!B98</f>
+        <v>29</v>
+      </c>
+      <c r="I98" s="40">
+        <f t="shared" si="7"/>
+        <v>26</v>
+      </c>
+      <c r="J98" s="41">
+        <f t="shared" si="8"/>
+        <v>89.65517241379311</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A99" s="27">
+        <v>98</v>
+      </c>
+      <c r="B99" s="28">
+        <f t="shared" si="4"/>
+        <v>46237</v>
+      </c>
+      <c r="C99" s="27"/>
+      <c r="D99" s="27"/>
+      <c r="E99" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F99" s="38">
+        <f t="shared" si="5"/>
+        <v>2.6440677966101696</v>
+      </c>
+      <c r="G99" s="39">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="H99" s="40">
+        <f>Лист2!B99</f>
+        <v>8</v>
+      </c>
+      <c r="I99" s="40">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="J99" s="41">
+        <f t="shared" si="8"/>
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A100" s="27">
+        <v>99</v>
+      </c>
+      <c r="B100" s="28">
+        <f t="shared" si="4"/>
+        <v>46244</v>
+      </c>
+      <c r="C100" s="27"/>
+      <c r="D100" s="27"/>
+      <c r="E100" s="30">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="F100" s="38">
+        <f t="shared" si="5"/>
+        <v>2.6610169491525424</v>
+      </c>
+      <c r="G100" s="39">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="H100" s="40">
+        <f>Лист2!B100</f>
+        <v>5</v>
+      </c>
+      <c r="I100" s="40">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="J100" s="41">
+        <f t="shared" si="8"/>
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>